--- a/data/availability/projects/ilcazar/glen.xlsx
+++ b/data/availability/projects/ilcazar/glen.xlsx
@@ -461,12 +461,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Glen latest availability</t>
+          <t>Updated inventory for glen</t>
         </is>
       </c>
     </row>
@@ -582,17 +582,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Glen</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Delivery 4 years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years · Maintenance 8%</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years; Maintenance 8%</t>
         </is>
       </c>
     </row>
@@ -632,17 +632,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Glen</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Delivery 4 years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years · Maintenance 8%</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years; Maintenance 8%</t>
         </is>
       </c>
     </row>
@@ -682,17 +682,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Glen</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Delivery 4 years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years · Maintenance 8%</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years; Maintenance 8%</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GLEN-2BD-130</t>
+          <t>GL-2BR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Glen</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -809,10 +809,14 @@
       <c r="G2" t="n">
         <v>130</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>130 SQM</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Landscape / View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -820,12 +824,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Delivery 4 years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years · Maintenance 8%</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years; Maintenance 8%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -847,12 +851,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GLEN-3BD-160</t>
+          <t>GL-3BR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Glen</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -866,10 +870,14 @@
       <c r="G3" t="n">
         <v>160</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>160 SQM</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Landscape / View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -877,12 +885,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Delivery 4 years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years · Maintenance 8%</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years; Maintenance 8%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -904,12 +912,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GLEN-PENT-171</t>
+          <t>GL-3BR-PH</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Glen</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -923,23 +931,27 @@
       <c r="G4" t="n">
         <v>171</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>171 SQM Penthouse</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Landscape / View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>13606094</v>
+        <v>13606093</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Delivery 4 years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years · Maintenance 8%</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years; Maintenance 8%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/data/availability/projects/ilcazar/glen.xlsx
+++ b/data/availability/projects/ilcazar/glen.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
